--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4192</v>
+        <v>6.452299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.825699999999999</v>
+        <v>8.125399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5935</v>
+        <v>-1.6732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9450999999999998</v>
+        <v>11.1975</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2747</v>
+        <v>1.4372</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3295</v>
+        <v>9.760300000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9199999999999999</v>
+        <v>11.4341</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7483</v>
+        <v>1.2291</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.8283</v>
+        <v>10.2049</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0252</v>
+        <v>-0.2365</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5265</v>
+        <v>0.2081</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5012</v>
+        <v>-0.4446</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2009</v>
+        <v>-6.2316</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2009</v>
+        <v>4.6737</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5941</v>
+        <v>-1.6352</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3076</v>
+        <v>-0.9682000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2865</v>
+        <v>-0.6672</v>
       </c>
       <c r="V2" t="n">
-        <v>1.88</v>
+        <v>-1.5521</v>
       </c>
       <c r="W2" t="n">
-        <v>4.799</v>
+        <v>3.891</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.9192</v>
+        <v>-5.4432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3379</v>
+        <v>6.4432</v>
       </c>
       <c r="E3" t="n">
-        <v>7.450799999999999</v>
+        <v>5.3197</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1129</v>
+        <v>1.1234</v>
       </c>
       <c r="G3" t="n">
-        <v>11.1622</v>
+        <v>1.067</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5167</v>
+        <v>3.3555</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6455</v>
+        <v>-2.2885</v>
       </c>
       <c r="J3" t="n">
-        <v>11.1094</v>
+        <v>1.2615</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1051</v>
+        <v>2.979</v>
       </c>
       <c r="L3" t="n">
-        <v>10.0043</v>
+        <v>-1.7175</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05279999999999999</v>
+        <v>-0.1945</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4116</v>
+        <v>0.3765</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3588</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.4018</v>
+        <v>-3.1158</v>
       </c>
       <c r="R3" t="n">
-        <v>4.801299999999999</v>
+        <v>3.1158</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.684</v>
+        <v>3.493</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0356</v>
+        <v>2.2898</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6484000000000001</v>
+        <v>1.2032</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5399</v>
+        <v>1.8832</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7788</v>
+        <v>4.8842</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.3187</v>
+        <v>-3.001</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7461</v>
+        <v>3.6792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07869999999999999</v>
+        <v>0.2322</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6674</v>
+        <v>3.4469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1178999999999999</v>
+        <v>0.1097999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9089</v>
+        <v>1.9156</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.791</v>
+        <v>-1.8058</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3945000000000001</v>
+        <v>-0.3114</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8815</v>
+        <v>0.9365</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.276</v>
+        <v>-1.248</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5124</v>
+        <v>0.4212</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0274</v>
+        <v>0.9789999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5149999999999999</v>
+        <v>-0.5578000000000001</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>2.008</v>
+        <v>1.9658</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4739</v>
+        <v>1.4647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.534</v>
+        <v>0.5011</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6202</v>
+        <v>1.6037</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="5">
@@ -799,31 +799,31 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2994</v>
+        <v>3.3553</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2994</v>
+        <v>3.3553</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2994</v>
+        <v>3.3553</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2994</v>
+        <v>3.3553</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4028</v>
+        <v>1.4278</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2409000000000001</v>
+        <v>0.2728</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6438</v>
+        <v>1.1552</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8529</v>
+        <v>5.9077</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2374</v>
+        <v>5.288500000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6155</v>
+        <v>0.6192</v>
       </c>
       <c r="J6" t="n">
-        <v>6.227600000000001</v>
+        <v>6.512700000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3821</v>
+        <v>5.5883</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8456</v>
+        <v>0.9244</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3747</v>
+        <v>-0.605</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1446</v>
+        <v>-0.2998</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2301</v>
+        <v>-0.3051</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.8011</v>
+        <v>-3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.002000000000001</v>
+        <v>-6.8158</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6701</v>
+        <v>1.6107</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2736</v>
+        <v>0.2962</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3965</v>
+        <v>1.3144</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3193</v>
+        <v>-2.3906</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5791</v>
+        <v>-2.6701</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3315</v>
+        <v>1.3467</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0316</v>
+        <v>-0.7942999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3632</v>
+        <v>2.141</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8805000000000001</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6892</v>
+        <v>-0.6635</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1911999999999999</v>
+        <v>-0.1848000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0068</v>
+        <v>-0.8405</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0525</v>
+        <v>-0.9543</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04569999999999996</v>
+        <v>0.1139</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1262</v>
+        <v>-0.007800000000000029</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3632</v>
+        <v>0.2907999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1881</v>
+        <v>-0.1946000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0247</v>
+        <v>-0.9801</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8365</v>
+        <v>0.7856000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,31 +1033,31 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8997999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8997999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8997999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8997999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8615999999999999</v>
+        <v>0.8329</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0934</v>
+        <v>-0.0839</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9550000000000001</v>
+        <v>0.9168000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8492</v>
+        <v>0.8266</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2269</v>
+        <v>0.2139</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6224000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1</v>
+        <v>0.1016</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7493000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2069</v>
+        <v>0.1934</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3877</v>
+        <v>-0.3832</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1934</v>
+        <v>-0.1855</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1943</v>
+        <v>-0.1977</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1225,19 +1225,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5318000000000003</v>
+        <v>-0.4756999999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4194</v>
+        <v>-4.661300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.8876</v>
+        <v>4.1856</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7249999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8734999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2167</v>
+        <v>-0.134</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5694</v>
+        <v>2.0258</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9124</v>
+        <v>1.1574</v>
       </c>
       <c r="L11" t="n">
-        <v>0.657</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9126</v>
+        <v>-1.3009</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0388</v>
+        <v>-0.2984</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8738</v>
+        <v>-1.0025</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2007</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.202</v>
+        <v>-7.0105</v>
       </c>
       <c r="R11" t="n">
-        <v>5.0015</v>
+        <v>4.868399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6119</v>
+        <v>1.552</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6464</v>
+        <v>-0.5667</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2583</v>
+        <v>2.1186</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5999</v>
+        <v>-0.6104999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9867</v>
+        <v>-3.7399</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.829700000000001</v>
+        <v>-5.201000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.843</v>
+        <v>1.4612</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3379</v>
+        <v>-2.1877</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.397</v>
+        <v>-1.4594</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9408000000000001</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2275</v>
+        <v>-1.8603</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9742999999999999</v>
+        <v>-0.9056</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2531</v>
+        <v>-0.9546</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1104</v>
+        <v>-0.3274</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4227</v>
+        <v>-0.5538000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3123</v>
+        <v>0.2265</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6002000000000001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R12" t="n">
-        <v>3.601</v>
+        <v>3.5052</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5683</v>
+        <v>-1.527</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7203</v>
+        <v>-1.6419</v>
       </c>
       <c r="U12" t="n">
-        <v>0.152</v>
+        <v>0.1149</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5196000000000001</v>
+        <v>0.5589</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3193</v>
+        <v>2.3905</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3961</v>
+        <v>-4.7432</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4528</v>
+        <v>-1.2284</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9433</v>
+        <v>-3.5149</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5532</v>
+        <v>-1.7351</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6411</v>
+        <v>-2.7428</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0878</v>
+        <v>1.0078</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4708000000000001</v>
+        <v>-0.3341</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1106</v>
+        <v>-0.9825</v>
       </c>
       <c r="L13" t="n">
-        <v>0.64</v>
+        <v>0.6484</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0825</v>
+        <v>-1.401</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5304</v>
+        <v>-1.7603</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4480000000000001</v>
+        <v>0.3593999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2012</v>
+        <v>4.0895</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8153</v>
+        <v>0.8187</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2185</v>
+        <v>1.2478</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4032</v>
+        <v>-0.4291</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.6588</v>
+        <v>-5.7742</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.6588</v>
+        <v>-5.7742</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.3026</v>
+        <v>-7.3727</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.0797</v>
+        <v>-6.721900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2228999999999999</v>
+        <v>-0.6507999999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.4049</v>
+        <v>-2.393</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01849999999999996</v>
+        <v>-0.1325000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3863</v>
+        <v>-2.2605</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.9587</v>
+        <v>-2.7433</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1381000000000001</v>
+        <v>-0.1102</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.8206</v>
+        <v>-2.6329</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.3502000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1197</v>
+        <v>-0.0222</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4343</v>
+        <v>0.3724</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4006</v>
+        <v>-2.3368</v>
       </c>
       <c r="R14" t="n">
-        <v>3.8011</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8392</v>
+        <v>-1.7897</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7203</v>
+        <v>-1.6419</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1189</v>
+        <v>-0.1479</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.459</v>
+        <v>-4.553199999999999</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.459</v>
+        <v>-4.553199999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>8.216700000000001</v>
+        <v>8.2546</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.657600000000003</v>
+        <v>-0.5314000000000032</v>
       </c>
       <c r="F15" t="n">
-        <v>12.8745</v>
+        <v>8.785900000000002</v>
       </c>
       <c r="G15" t="n">
-        <v>16.6068</v>
+        <v>16.9406</v>
       </c>
       <c r="H15" t="n">
-        <v>9.491900000000001</v>
+        <v>9.303100000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>7.115200000000002</v>
+        <v>7.637599999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>17.0673</v>
+        <v>19.5172</v>
       </c>
       <c r="K15" t="n">
-        <v>8.9735</v>
+        <v>10.1898</v>
       </c>
       <c r="L15" t="n">
-        <v>8.094099999999999</v>
+        <v>9.327600000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4604</v>
+        <v>-2.5767</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5188</v>
+        <v>-0.8867000000000003</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9788</v>
+        <v>-1.6897</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.001000000000001</v>
+        <v>-2.920999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-35.0098</v>
+        <v>-34.0789</v>
       </c>
       <c r="R15" t="n">
-        <v>32.0091</v>
+        <v>31.1579</v>
       </c>
       <c r="S15" t="n">
-        <v>3.967600000000001</v>
+        <v>3.8487</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1316</v>
+        <v>-0.7476</v>
       </c>
       <c r="U15" t="n">
-        <v>5.099</v>
+        <v>4.5959</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.3573</v>
+        <v>-9.613699999999998</v>
       </c>
       <c r="W15" t="n">
-        <v>14.4162</v>
+        <v>14.7774</v>
       </c>
       <c r="X15" t="n">
-        <v>-23.7737</v>
+        <v>-24.3912</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.452299999999999</v>
+        <v>7.5629</v>
       </c>
       <c r="E2" t="n">
-        <v>8.125399999999999</v>
+        <v>8.623799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6732</v>
+        <v>-1.0609</v>
       </c>
       <c r="G2" t="n">
         <v>11.1975</v>
@@ -610,13 +610,13 @@
         <v>4.6737</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6352</v>
+        <v>-0.5246999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9682000000000001</v>
+        <v>-0.4698</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6672</v>
+        <v>-0.0549</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5521</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4432</v>
+        <v>4.8853</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3197</v>
+        <v>4.1236</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1234</v>
+        <v>0.7616999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.067</v>
@@ -688,13 +688,13 @@
         <v>3.1158</v>
       </c>
       <c r="S3" t="n">
-        <v>3.493</v>
+        <v>1.9352</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2898</v>
+        <v>1.0937</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2032</v>
+        <v>0.8414</v>
       </c>
       <c r="V3" t="n">
         <v>1.8832</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6792</v>
+        <v>3.3553</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2322</v>
+        <v>3.3553</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4469</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1097999999999999</v>
+        <v>3.3553</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9156</v>
+        <v>0.9237</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8058</v>
+        <v>2.4316</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3114</v>
+        <v>3.3553</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9365</v>
+        <v>0.9237</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.248</v>
+        <v>2.4316</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4212</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9789999999999999</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5578000000000001</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1421</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1421</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9658</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4647</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5011</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6037</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3553</v>
+        <v>2.8161</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3553</v>
+        <v>-0.603</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3.4191</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3553</v>
+        <v>0.1097999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9237</v>
+        <v>1.9156</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4316</v>
+        <v>-1.8058</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3553</v>
+        <v>-0.3114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9237</v>
+        <v>0.9365</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4316</v>
+        <v>-1.248</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.4212</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.9789999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.5578000000000001</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.1027</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.4732</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.6037</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4278</v>
+        <v>1.9834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2728</v>
+        <v>0.06489999999999996</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1552</v>
+        <v>1.9184</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9077</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>5.288500000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6192</v>
+        <v>-0.1848000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>6.512700000000001</v>
+        <v>-0.8405</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5883</v>
+        <v>-0.9543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9244</v>
+        <v>0.1139</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.605</v>
+        <v>-0.007800000000000029</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2998</v>
+        <v>0.2907999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3051</v>
+        <v>-0.2986</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.7</v>
+        <v>1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.8158</v>
+        <v>-0.1947</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1158</v>
+        <v>1.3632</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6107</v>
+        <v>0.4421</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2962</v>
+        <v>-0.1209</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3144</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3906</v>
+        <v>1.2211</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3467</v>
+        <v>1.7369</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7942999999999999</v>
+        <v>0.6715</v>
       </c>
       <c r="F7" t="n">
-        <v>2.141</v>
+        <v>1.0655</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8483000000000001</v>
+        <v>5.9077</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6635</v>
+        <v>5.288500000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1848000000000001</v>
+        <v>0.6192</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8405</v>
+        <v>6.512700000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9543</v>
+        <v>5.5883</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1139</v>
+        <v>0.9244</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.007800000000000029</v>
+        <v>-0.605</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2907999999999999</v>
+        <v>-0.2998</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2986</v>
+        <v>-0.3051</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1684</v>
+        <v>-3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1947</v>
+        <v>-6.8158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3632</v>
+        <v>3.1158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1946000000000001</v>
+        <v>1.9196</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9801</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7856000000000001</v>
+        <v>1.2247</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2211</v>
+        <v>-2.3906</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.6701</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8329</v>
+        <v>0.8769</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0839</v>
+        <v>0.01579999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9168000000000001</v>
+        <v>0.8612</v>
       </c>
       <c r="G9" t="n">
         <v>0.8266</v>
@@ -1156,13 +1156,13 @@
         <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3832</v>
+        <v>-0.3391</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1855</v>
+        <v>-0.0858</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1977</v>
+        <v>-0.2533</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4756999999999998</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.661300000000001</v>
+        <v>-4.4001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1856</v>
+        <v>3.6506</v>
       </c>
       <c r="G11" t="n">
         <v>0.7249999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>4.868399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.552</v>
+        <v>1.2783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5667</v>
+        <v>-0.3055</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1186</v>
+        <v>1.5837</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6104999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7399</v>
+        <v>-2.7083</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.201000000000001</v>
+        <v>-4.4414</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4612</v>
+        <v>1.7332</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1877</v>
@@ -1390,13 +1390,13 @@
         <v>3.5052</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.527</v>
+        <v>-0.4953</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6419</v>
+        <v>-0.8823</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1149</v>
+        <v>0.3869</v>
       </c>
       <c r="V12" t="n">
         <v>0.5589</v>
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7432</v>
+        <v>-5.3218</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2284</v>
+        <v>-2.5242</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5149</v>
+        <v>-2.7976</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7351</v>
@@ -1468,13 +1468,13 @@
         <v>4.0895</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8187</v>
+        <v>0.2402</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2478</v>
+        <v>-0.04799999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4291</v>
+        <v>0.2882</v>
       </c>
       <c r="V13" t="n">
         <v>-5.7742</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.3727</v>
+        <v>-6.257700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.721900000000001</v>
+        <v>-5.9624</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6507999999999998</v>
+        <v>-0.2952999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-2.393</v>
@@ -1546,13 +1546,13 @@
         <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7897</v>
+        <v>-0.6746000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6419</v>
+        <v>-0.8823</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1479</v>
+        <v>0.2076</v>
       </c>
       <c r="V14" t="n">
         <v>-4.553199999999999</v>
@@ -1579,13 +1579,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>8.2546</v>
+        <v>9.228199999999994</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5314000000000032</v>
+        <v>-0.2222000000000017</v>
       </c>
       <c r="F15" t="n">
-        <v>8.785900000000002</v>
+        <v>9.4506</v>
       </c>
       <c r="G15" t="n">
         <v>16.9406</v>
@@ -1624,13 +1624,13 @@
         <v>31.1579</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8487</v>
+        <v>4.8226</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7476</v>
+        <v>-0.4382000000000003</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5959</v>
+        <v>5.2605</v>
       </c>
       <c r="V15" t="n">
         <v>-9.613699999999998</v>
